--- a/outputs/daily/hr_rankings_2026-07-16.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-16.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>65</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>49.2</v>
       </c>
       <c r="R2" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -1036,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>64</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>35.4</v>
       </c>
       <c r="R3" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1272,8 +1272,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -1312,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>52.1</v>
+        <v>56.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>47.2</v>
       </c>
       <c r="R4" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>75</v>
@@ -1373,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1548,8 +1552,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -1588,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1612,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>51.8</v>
+        <v>56.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1636,10 +1648,10 @@
         <v>49.2</v>
       </c>
       <c r="R5" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1649,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1824,8 +1832,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -1864,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1888,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>51.5</v>
+        <v>56.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,7 +1918,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1912,10 +1928,10 @@
         <v>35.4</v>
       </c>
       <c r="R6" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -1925,39 +1941,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2100,8 +2112,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -2140,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2164,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>50.2</v>
+        <v>54.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,7 +2198,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2188,10 +2208,10 @@
         <v>49.2</v>
       </c>
       <c r="R7" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -2201,39 +2221,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -2376,8 +2392,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -2416,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2440,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>49.4</v>
+        <v>54</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,7 +2478,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2464,10 +2488,10 @@
         <v>49.2</v>
       </c>
       <c r="R8" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S8" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -2477,39 +2501,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2652,8 +2672,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -2692,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2716,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>47.4</v>
+        <v>52</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2740,10 +2768,10 @@
         <v>49.2</v>
       </c>
       <c r="R9" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S9" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
@@ -2753,39 +2781,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2928,8 +2952,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -2968,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2992,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>47.4</v>
+        <v>52</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3048,10 @@
         <v>35.4</v>
       </c>
       <c r="R10" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -3029,39 +3061,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3204,8 +3232,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -3244,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>46.5</v>
+        <v>51.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,7 +3318,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3292,10 +3328,10 @@
         <v>49.2</v>
       </c>
       <c r="R11" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S11" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
@@ -3305,39 +3341,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3480,8 +3512,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -3520,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3544,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>45.7</v>
+        <v>50.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,7 +3598,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3568,10 +3608,10 @@
         <v>49.2</v>
       </c>
       <c r="R12" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S12" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -3581,39 +3621,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3756,8 +3792,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -3796,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3820,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>40.9</v>
+        <v>45.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,7 +3878,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3844,10 +3888,10 @@
         <v>35.4</v>
       </c>
       <c r="R13" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -3857,39 +3901,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4032,8 +4072,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -4072,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4096,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>40.1</v>
+        <v>44.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,7 +4158,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4120,10 +4168,10 @@
         <v>35.4</v>
       </c>
       <c r="R14" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S14" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T14" t="n">
         <v>50</v>
@@ -4133,39 +4181,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4308,8 +4352,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -4348,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4372,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>39.8</v>
+        <v>44.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,7 +4438,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4396,10 +4448,10 @@
         <v>47.2</v>
       </c>
       <c r="R15" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -4409,39 +4461,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4584,8 +4632,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -4604,7 +4660,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gabriel Rincones</t>
+          <t>Gabriel Rincones Jr.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4624,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4648,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>39.8</v>
+        <v>44.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,7 +4718,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -4672,10 +4728,10 @@
         <v>35.4</v>
       </c>
       <c r="R16" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
@@ -4685,39 +4741,35 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -4860,8 +4912,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -4900,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4924,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>39.4</v>
+        <v>44</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,7 +4998,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -4948,10 +5008,10 @@
         <v>35.4</v>
       </c>
       <c r="R17" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>50</v>
@@ -4961,39 +5021,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5136,8 +5192,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -5176,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5200,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.9</v>
+        <v>43.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,7 +5278,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -5224,10 +5288,10 @@
         <v>35.4</v>
       </c>
       <c r="R18" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S18" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
@@ -5237,39 +5301,35 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5412,8 +5472,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -5452,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5476,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>31.3</v>
+        <v>35.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5500,10 +5568,10 @@
         <v>35.4</v>
       </c>
       <c r="R19" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>80</v>
@@ -5513,39 +5581,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -5688,8 +5752,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -6054,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6078,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>65</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6174,10 @@
         <v>49.2</v>
       </c>
       <c r="R2" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -6115,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6290,8 +6358,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -6330,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6354,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>64</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6454,10 @@
         <v>35.4</v>
       </c>
       <c r="R3" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6391,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -6566,8 +6638,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -6606,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6630,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>52.1</v>
+        <v>56.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6734,10 @@
         <v>47.2</v>
       </c>
       <c r="R4" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>75</v>
@@ -6667,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6842,8 +6918,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -6882,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6906,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>51.8</v>
+        <v>56.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -6930,10 +7014,10 @@
         <v>49.2</v>
       </c>
       <c r="R5" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -6943,39 +7027,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7118,8 +7198,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -7158,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7182,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>51.5</v>
+        <v>56.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,7 +7284,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7206,10 +7294,10 @@
         <v>35.4</v>
       </c>
       <c r="R6" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -7219,39 +7307,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7394,8 +7478,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -7434,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7458,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>50.2</v>
+        <v>54.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,7 +7564,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -7482,10 +7574,10 @@
         <v>49.2</v>
       </c>
       <c r="R7" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -7495,39 +7587,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7670,8 +7758,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -7710,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7734,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>49.4</v>
+        <v>54</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,7 +7844,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7758,10 +7854,10 @@
         <v>49.2</v>
       </c>
       <c r="R8" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S8" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -7771,39 +7867,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7946,8 +8038,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -7986,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8010,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>47.4</v>
+        <v>52</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,7 +8124,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8034,10 +8134,10 @@
         <v>49.2</v>
       </c>
       <c r="R9" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S9" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
@@ -8047,39 +8147,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8222,8 +8318,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -8262,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8286,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>47.4</v>
+        <v>52</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8414,10 @@
         <v>35.4</v>
       </c>
       <c r="R10" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -8323,39 +8427,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -8498,8 +8598,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -8538,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>46.5</v>
+        <v>51.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,7 +8684,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8586,10 +8694,10 @@
         <v>49.2</v>
       </c>
       <c r="R11" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S11" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
@@ -8599,39 +8707,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8774,8 +8878,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -8814,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8838,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>45.7</v>
+        <v>50.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,7 +8964,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -8862,10 +8974,10 @@
         <v>49.2</v>
       </c>
       <c r="R12" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S12" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -8875,39 +8987,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9050,8 +9158,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -9090,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9114,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>40.9</v>
+        <v>45.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,7 +9244,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -9138,10 +9254,10 @@
         <v>35.4</v>
       </c>
       <c r="R13" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -9151,39 +9267,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9326,8 +9438,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -9366,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9390,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>40.1</v>
+        <v>44.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,7 +9524,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9414,10 +9534,10 @@
         <v>35.4</v>
       </c>
       <c r="R14" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S14" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T14" t="n">
         <v>50</v>
@@ -9427,39 +9547,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9602,8 +9718,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -9642,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9666,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>39.8</v>
+        <v>44.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,7 +9804,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -9690,10 +9814,10 @@
         <v>47.2</v>
       </c>
       <c r="R15" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -9703,39 +9827,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9878,8 +9998,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -9898,7 +10026,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gabriel Rincones</t>
+          <t>Gabriel Rincones Jr.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9918,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -9942,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>39.8</v>
+        <v>44.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,7 +10084,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -9966,10 +10094,10 @@
         <v>35.4</v>
       </c>
       <c r="R16" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
@@ -9979,39 +10107,35 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -10154,8 +10278,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -10194,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10218,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>39.4</v>
+        <v>44</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,7 +10364,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -10242,10 +10374,10 @@
         <v>35.4</v>
       </c>
       <c r="R17" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>50</v>
@@ -10255,39 +10387,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10430,8 +10558,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -10470,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10494,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.9</v>
+        <v>43.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,7 +10644,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -10518,10 +10654,10 @@
         <v>35.4</v>
       </c>
       <c r="R18" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S18" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
@@ -10531,39 +10667,35 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10706,8 +10838,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -10746,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10770,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>31.3</v>
+        <v>35.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -10794,10 +10934,10 @@
         <v>35.4</v>
       </c>
       <c r="R19" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>80</v>
@@ -10807,39 +10947,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -10982,8 +11118,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>

--- a/outputs/daily/hr_rankings_2026-07-16.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-16.xlsx
@@ -755,7 +755,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -10041,7 +10041,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
